--- a/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,12 +571,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -584,29 +584,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00981A(141,000)、00403A(40,000)</t>
+          <t>00982A(9,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(-29,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>日月光投</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -614,29 +614,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>00981A(141,000)、00403A(40,000)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>00991A(-1,491,000)、00982A(-57,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>日月光投</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,29 +644,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00981A(44,000)、00403A(40,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00991A(-1,491,000)、00982A(-57,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -674,45 +674,105 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00991A(100,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>00982A(-16,000)</t>
+          <t>00981A(-350,000)、00985A(-60,000)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>00981A(44,000)、00403A(40,000)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00991A(100,000)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>00982A(-16,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>7769</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>鴻勁精密</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>00985A(13,000)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>00982A(全數賣出)</t>
         </is>

--- a/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,29 +464,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00980A(351,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00982A(-3,824,000)、00403A(-10,000,000)</t>
+          <t>00985A(-204,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -504,19 +504,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00403A(-3,000,000)、00985A(-204,000)</t>
+          <t>00981A(-200,000)、00980A(-5,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -524,257 +524,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00982A(213,000)、00985A(96,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>00981A(-200,000)、00991A(-100,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>00982A(9,000)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>00985A(-29,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>00981A(141,000)、00403A(40,000)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>日月光投</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>00991A(-1,491,000)、00982A(-57,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
           <t>00981A(-350,000)、00985A(-60,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>00981A(44,000)、00403A(40,000)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>台燿科技</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>00991A(100,000)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>00982A(-16,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>鴻勁精密</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>00985A(13,000)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>00982A(全數賣出)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00985A(-204,000)</t>
+          <t>00403A(-3,000,000)、00985A(-204,000)</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -504,37 +504,307 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00981A(-200,000)、00980A(-5,000)</t>
+          <t>00981A(-200,000)、00991A(-100,000)、00980A(-5,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>00991A(100,000)、00980A(22,000)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>00982A(-16,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>00982A(-3,824,000)、00403A(-10,000,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>00980A(81,000)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>00982A(全數賣出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>00982A(213,000)、00985A(96,000)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>00982A(9,000)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>00985A(-29,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>00981A(141,000)、00403A(40,000)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>日月光投</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>00991A(-1,491,000)、00982A(-57,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>6187</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C11" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>全部減碼</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>00981A(-350,000)、00985A(-60,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>00981A(44,000)、00403A(40,000)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>00985A(13,000)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>00982A(全數賣出)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,29 +464,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00980A(351,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00403A(-3,000,000)、00985A(-204,000)</t>
+          <t>• 00981A(-200,000)
+• 00991A(-100,000)
+• 00980A(-5,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -494,33 +496,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>• 00991A(100,000)
+• 00980A(22,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00981A(-200,000)、00991A(-100,000)、00980A(-5,000)</t>
+          <t>• 00982A(-16,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -529,24 +532,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00991A(100,000)、00980A(22,000)</t>
+          <t>• 00980A(81,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00982A(-16,000)</t>
+          <t>• 00982A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>日月光投</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -564,247 +567,8 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00982A(-3,824,000)、00403A(-10,000,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>國巨</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>00980A(81,000)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>00982A(全數賣出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>00982A(213,000)、00985A(96,000)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>00982A(9,000)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>00985A(-29,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>00981A(141,000)、00403A(40,000)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>日月光投</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>00991A(-1,491,000)、00982A(-57,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>00981A(-350,000)、00985A(-60,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>00981A(44,000)、00403A(40,000)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>鴻勁精密</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>00985A(13,000)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>00982A(全數賣出)</t>
+          <t>• 00991A(-1,491,000)
+• 00982A(-57,000)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,12 +514,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -527,29 +527,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>• 00980A(81,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>• 00982A(全數賣出)</t>
+          <t>• 00982A(-3,824,000)
+• 00403A(-10,000,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>日月光投</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -557,18 +558,140 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>• 00980A(81,000)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>• 00982A(全數賣出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>• 00980A(351,000)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>• 00403A(-3,000,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>• 00981A(141,000)
+• 00403A(40,000)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>日月光投</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>全部減碼</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>• 00991A(-1,491,000)
 • 00982A(-57,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>• 00981A(44,000)
+• 00403A(40,000)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,19 +464,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00980A(351,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>• 00981A(-200,000)
-• 00991A(-100,000)
-• 00980A(-5,000)</t>
+          <t>00403A(-3,000,000)、00985A(-204,000)</t>
         </is>
       </c>
     </row>
@@ -501,13 +499,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>• 00991A(100,000)
-• 00980A(22,000)</t>
+          <t>00980A(22,000)、00403A(120,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>• 00982A(-16,000)</t>
+          <t>00982A(-16,000)</t>
         </is>
       </c>
     </row>
@@ -537,8 +534,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>• 00982A(-3,824,000)
-• 00403A(-10,000,000)</t>
+          <t>00982A(-3,824,000)、00403A(-10,000,000)</t>
         </is>
       </c>
     </row>
@@ -563,24 +559,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>• 00980A(81,000)</t>
+          <t>00980A(81,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>• 00982A(全數賣出)</t>
+          <t>00982A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -593,24 +589,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>• 00980A(351,000)</t>
+          <t>00982A(7,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>• 00403A(-3,000,000)</t>
+          <t>00981A(-293,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -623,8 +619,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>• 00981A(141,000)
-• 00403A(40,000)</t>
+          <t>00982A(213,000)、00985A(96,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -636,12 +631,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>日月光投</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -659,39 +654,157 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>• 00991A(-1,491,000)
-• 00982A(-57,000)</t>
+          <t>00981A(-200,000)、00980A(-5,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>00982A(9,000)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>00985A(-29,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>00981A(141,000)、00403A(100,000)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>00981A(-350,000)、00985A(-60,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>6223</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>旺矽</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>全部加碼</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>• 00981A(44,000)
-• 00403A(40,000)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>00981A(44,000)、00403A(40,000)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>00985A(13,000)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>00982A(全數賣出)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-21_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,20 +456,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00980A(351,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -481,42 +481,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00980A(22,000)、00403A(120,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00982A(-16,000)</t>
+          <t>00981A(-200,000)、00991A(-100,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -524,29 +524,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>00981A(141,000)、00403A(100,000)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>00982A(-3,824,000)、00403A(-10,000,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -554,29 +554,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00980A(81,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00982A(全數賣出)</t>
+          <t>00981A(-350,000)、00985A(-60,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -584,29 +584,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00982A(7,000)</t>
+          <t>00981A(44,000)、00403A(40,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00981A(-293,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00982A(213,000)、00985A(96,000)</t>
+          <t>00991A(100,000)、00403A(120,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -631,12 +631,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>鴻勁精密</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,167 +644,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(13,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00981A(-200,000)、00980A(-5,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>00982A(9,000)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>00985A(-29,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>00981A(141,000)、00403A(100,000)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>00981A(-350,000)、00985A(-60,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>00981A(44,000)、00403A(40,000)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>鴻勁精密</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>00985A(13,000)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>00982A(全數賣出)</t>
+          <t>00991A(-20,000)</t>
         </is>
       </c>
     </row>
